--- a/Team-Data/2007-08/4-4-2007-08.xlsx
+++ b/Team-Data/2007-08/4-4-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,46 +728,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
         <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>0.461</v>
+        <v>0.467</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J2" t="n">
         <v>79.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O2" t="n">
         <v>21.1</v>
       </c>
       <c r="P2" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R2" t="n">
         <v>12.3</v>
@@ -709,16 +776,16 @@
         <v>30</v>
       </c>
       <c r="T2" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U2" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V2" t="n">
         <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X2" t="n">
         <v>5.6</v>
@@ -733,22 +800,22 @@
         <v>21.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC2" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
         <v>4</v>
@@ -769,7 +836,7 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
         <v>5</v>
@@ -787,7 +854,7 @@
         <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
         <v>11</v>
@@ -796,16 +863,16 @@
         <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
         <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
         <v>9</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
         <v>19</v>
@@ -942,7 +1009,7 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL3" t="n">
         <v>9</v>
@@ -987,13 +1054,13 @@
         <v>16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA3" t="n">
         <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
         <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>0.382</v>
+        <v>0.373</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,7 +1110,7 @@
         <v>35.8</v>
       </c>
       <c r="J4" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K4" t="n">
         <v>0.449</v>
@@ -1055,7 +1122,7 @@
         <v>17.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O4" t="n">
         <v>18.2</v>
@@ -1064,19 +1131,19 @@
         <v>25.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.711</v>
+        <v>0.71</v>
       </c>
       <c r="R4" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S4" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T4" t="n">
         <v>40.5</v>
       </c>
       <c r="U4" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V4" t="n">
         <v>14.7</v>
@@ -1091,19 +1158,19 @@
         <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.5</v>
+        <v>-4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1121,10 +1188,10 @@
         <v>25</v>
       </c>
       <c r="AJ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK4" t="n">
         <v>19</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1145,7 +1212,7 @@
         <v>29</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>23</v>
@@ -1154,25 +1221,25 @@
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -1285,19 +1352,19 @@
         <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1321,13 +1388,13 @@
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
         <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS5" t="n">
         <v>18</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1479,7 +1546,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI6" t="n">
         <v>23</v>
@@ -1503,7 +1570,7 @@
         <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1536,13 +1603,13 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB6" t="n">
         <v>19</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" t="n">
         <v>47</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>0.618</v>
+        <v>0.627</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J7" t="n">
         <v>79.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L7" t="n">
         <v>6</v>
@@ -1604,22 +1671,22 @@
         <v>0.351</v>
       </c>
       <c r="O7" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="P7" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>10.8</v>
       </c>
       <c r="S7" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T7" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U7" t="n">
         <v>20.9</v>
@@ -1637,34 +1704,34 @@
         <v>4.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA7" t="n">
         <v>21.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.3</v>
+        <v>100.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
@@ -1673,7 +1740,7 @@
         <v>9</v>
       </c>
       <c r="AL7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM7" t="n">
         <v>19</v>
@@ -1691,7 +1758,7 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS7" t="n">
         <v>6</v>
@@ -1715,10 +1782,10 @@
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -1831,19 +1898,19 @@
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1861,7 +1928,7 @@
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
         <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>0.72</v>
+        <v>0.716</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1956,7 +2023,7 @@
         <v>79.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
@@ -1968,52 +2035,52 @@
         <v>0.372</v>
       </c>
       <c r="O9" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P9" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R9" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S9" t="n">
         <v>29.3</v>
       </c>
       <c r="T9" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U9" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V9" t="n">
         <v>11.6</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y9" t="n">
         <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB9" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2040,10 +2107,10 @@
         <v>18</v>
       </c>
       <c r="AM9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO9" t="n">
         <v>18</v>
@@ -2061,7 +2128,7 @@
         <v>25</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
@@ -2073,19 +2140,19 @@
         <v>16</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY9" t="n">
         <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
         <v>25</v>
       </c>
       <c r="BB9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -2117,43 +2184,43 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
         <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>0.605</v>
+        <v>0.6</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="J10" t="n">
         <v>89.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L10" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O10" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P10" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q10" t="n">
         <v>0.753</v>
@@ -2162,16 +2229,16 @@
         <v>12.5</v>
       </c>
       <c r="S10" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T10" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="U10" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V10" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W10" t="n">
         <v>9.1</v>
@@ -2186,19 +2253,19 @@
         <v>22.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>110.6</v>
+        <v>110.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2207,7 +2274,7 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2228,10 +2295,10 @@
         <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
         <v>19</v>
@@ -2240,7 +2307,7 @@
         <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
@@ -2249,7 +2316,7 @@
         <v>10</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
         <v>2</v>
@@ -2264,7 +2331,7 @@
         <v>27</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.671</v>
+        <v>0.667</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J11" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K11" t="n">
         <v>0.449</v>
@@ -2326,31 +2393,31 @@
         <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O11" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P11" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R11" t="n">
         <v>12.3</v>
       </c>
       <c r="S11" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T11" t="n">
         <v>44.5</v>
       </c>
       <c r="U11" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V11" t="n">
         <v>13.9</v>
@@ -2365,19 +2432,19 @@
         <v>4.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA11" t="n">
         <v>19.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>96.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
@@ -2389,7 +2456,7 @@
         <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>17</v>
@@ -2407,7 +2474,7 @@
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
@@ -2416,7 +2483,7 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR11" t="n">
         <v>8</v>
@@ -2425,7 +2492,7 @@
         <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="n">
         <v>14</v>
@@ -2434,10 +2501,10 @@
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
@@ -2449,7 +2516,7 @@
         <v>26</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
         <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>0.421</v>
+        <v>0.413</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J12" t="n">
-        <v>85.3</v>
+        <v>85.5</v>
       </c>
       <c r="K12" t="n">
         <v>0.442</v>
@@ -2508,22 +2575,22 @@
         <v>9.1</v>
       </c>
       <c r="M12" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O12" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S12" t="n">
         <v>31.9</v>
@@ -2535,7 +2602,7 @@
         <v>22.5</v>
       </c>
       <c r="V12" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W12" t="n">
         <v>7.7</v>
@@ -2550,16 +2617,16 @@
         <v>23.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB12" t="n">
         <v>103.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.9</v>
+        <v>-2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2580,7 +2647,7 @@
         <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
@@ -2598,7 +2665,7 @@
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2613,7 +2680,7 @@
         <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,22 +2820,22 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
         <v>28</v>
       </c>
       <c r="AM13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN13" t="n">
         <v>29</v>
@@ -2786,13 +2853,13 @@
         <v>25</v>
       </c>
       <c r="AS13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
         <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV13" t="n">
         <v>14</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" t="n">
         <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,10 +2930,10 @@
         <v>39.6</v>
       </c>
       <c r="J14" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
         <v>7.9</v>
@@ -2875,25 +2942,25 @@
         <v>21.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O14" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="P14" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R14" t="n">
         <v>10.9</v>
       </c>
       <c r="S14" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T14" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U14" t="n">
         <v>24.3</v>
@@ -2914,28 +2981,28 @@
         <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.5</v>
+        <v>108.4</v>
       </c>
       <c r="AC14" t="n">
         <v>6.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2944,7 +3011,7 @@
         <v>6</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" t="n">
         <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>0.263</v>
+        <v>0.267</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L15" t="n">
         <v>7.5</v>
@@ -3057,16 +3124,16 @@
         <v>21.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O15" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.728</v>
+        <v>0.729</v>
       </c>
       <c r="R15" t="n">
         <v>10.2</v>
@@ -3078,10 +3145,10 @@
         <v>41.5</v>
       </c>
       <c r="U15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W15" t="n">
         <v>6.1</v>
@@ -3093,19 +3160,19 @@
         <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA15" t="n">
         <v>22.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.4</v>
+        <v>100.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,10 +3184,10 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ15" t="n">
         <v>13</v>
@@ -3135,7 +3202,7 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO15" t="n">
         <v>19</v>
@@ -3147,13 +3214,13 @@
         <v>23</v>
       </c>
       <c r="AR15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU15" t="n">
         <v>29</v>
@@ -3165,19 +3232,19 @@
         <v>29</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY15" t="n">
         <v>18</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
         <v>7</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
         <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>0.171</v>
+        <v>0.173</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,67 +3294,67 @@
         <v>34.4</v>
       </c>
       <c r="J16" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="K16" t="n">
         <v>0.446</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.356</v>
+        <v>0.35</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.723</v>
+        <v>0.724</v>
       </c>
       <c r="R16" t="n">
         <v>9.1</v>
       </c>
       <c r="S16" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="T16" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="U16" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V16" t="n">
         <v>14.9</v>
       </c>
       <c r="W16" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X16" t="n">
         <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z16" t="n">
         <v>20.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>91.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>-9</v>
+        <v>-8.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
         <v>30</v>
@@ -3317,22 +3384,22 @@
         <v>23</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>25</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" t="n">
         <v>26</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>0.347</v>
+        <v>0.351</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,7 +3479,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L17" t="n">
         <v>5.5</v>
@@ -3421,13 +3488,13 @@
         <v>16.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q17" t="n">
         <v>0.736</v>
@@ -3439,37 +3506,37 @@
         <v>28.7</v>
       </c>
       <c r="T17" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U17" t="n">
         <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X17" t="n">
         <v>4.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA17" t="n">
         <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.4</v>
+        <v>-6.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3484,49 +3551,49 @@
         <v>10</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ17" t="n">
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>24</v>
       </c>
       <c r="AM17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO17" t="n">
         <v>22</v>
       </c>
       <c r="AP17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV17" t="n">
         <v>15</v>
       </c>
-      <c r="AV17" t="n">
-        <v>18</v>
-      </c>
       <c r="AW17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX17" t="n">
         <v>20</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" t="n">
         <v>19</v>
       </c>
       <c r="F18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
-        <v>0.253</v>
+        <v>0.257</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
@@ -3591,34 +3658,34 @@
         <v>37</v>
       </c>
       <c r="J18" t="n">
-        <v>82.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="L18" t="n">
         <v>5.3</v>
       </c>
       <c r="M18" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="N18" t="n">
         <v>0.344</v>
       </c>
       <c r="O18" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.734</v>
+        <v>0.736</v>
       </c>
       <c r="R18" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S18" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
         <v>41.1</v>
@@ -3627,31 +3694,31 @@
         <v>19.9</v>
       </c>
       <c r="V18" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W18" t="n">
         <v>7.6</v>
       </c>
       <c r="X18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y18" t="n">
         <v>5.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.9</v>
+        <v>-6.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3672,7 +3739,7 @@
         <v>9</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL18" t="n">
         <v>25</v>
@@ -3690,22 +3757,22 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
         <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU18" t="n">
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" t="n">
         <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>0.408</v>
+        <v>0.413</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
@@ -3779,31 +3846,31 @@
         <v>0.442</v>
       </c>
       <c r="L19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O19" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="P19" t="n">
         <v>27.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R19" t="n">
         <v>11.4</v>
       </c>
       <c r="S19" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T19" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="U19" t="n">
         <v>23.3</v>
@@ -3821,31 +3888,31 @@
         <v>4.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA19" t="n">
         <v>22.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5</v>
+        <v>-4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI19" t="n">
         <v>28</v>
@@ -3854,10 +3921,10 @@
         <v>25</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM19" t="n">
         <v>18</v>
@@ -3881,7 +3948,7 @@
         <v>13</v>
       </c>
       <c r="AT19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
@@ -3890,16 +3957,16 @@
         <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F20" t="n">
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.707</v>
+        <v>0.703</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3958,7 +4025,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L20" t="n">
         <v>7.8</v>
@@ -3967,25 +4034,25 @@
         <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.393</v>
+        <v>0.392</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P20" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R20" t="n">
         <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T20" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U20" t="n">
         <v>21.6</v>
@@ -4000,7 +4067,7 @@
         <v>3.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z20" t="n">
         <v>18.7</v>
@@ -4009,13 +4076,13 @@
         <v>19.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC20" t="n">
         <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
         <v>3</v>
@@ -4033,7 +4100,7 @@
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
         <v>8</v>
@@ -4045,7 +4112,7 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
         <v>29</v>
@@ -4057,13 +4124,13 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU20" t="n">
         <v>13</v>
@@ -4072,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>9</v>
       </c>
       <c r="BC20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" t="n">
-        <v>0.263</v>
+        <v>0.267</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J21" t="n">
         <v>81.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L21" t="n">
         <v>5.8</v>
@@ -4149,31 +4216,31 @@
         <v>17.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O21" t="n">
         <v>18.8</v>
       </c>
       <c r="P21" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.724</v>
+        <v>0.723</v>
       </c>
       <c r="R21" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S21" t="n">
         <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U21" t="n">
         <v>18.6</v>
       </c>
       <c r="V21" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W21" t="n">
         <v>6.3</v>
@@ -4188,16 +4255,16 @@
         <v>21.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>-7</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4212,13 +4279,13 @@
         <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ21" t="n">
         <v>14</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL21" t="n">
         <v>21</v>
@@ -4230,22 +4297,22 @@
         <v>28</v>
       </c>
       <c r="AO21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR21" t="n">
         <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
         <v>30</v>
@@ -4254,7 +4321,7 @@
         <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4269,7 +4336,7 @@
         <v>19</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>4.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>9</v>
@@ -4397,7 +4464,7 @@
         <v>12</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4418,19 +4485,19 @@
         <v>3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR22" t="n">
         <v>28</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>15</v>
       </c>
       <c r="AU22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F23" t="n">
         <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>0.513</v>
+        <v>0.507</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4504,7 +4571,7 @@
         <v>81</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
         <v>3.6</v>
@@ -4513,7 +4580,7 @@
         <v>11.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.317</v>
+        <v>0.316</v>
       </c>
       <c r="O23" t="n">
         <v>18.7</v>
@@ -4522,22 +4589,22 @@
         <v>26.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.71</v>
+        <v>0.707</v>
       </c>
       <c r="R23" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="S23" t="n">
         <v>28.9</v>
       </c>
       <c r="T23" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W23" t="n">
         <v>8.6</v>
@@ -4552,16 +4619,16 @@
         <v>19.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>14</v>
@@ -4594,7 +4661,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
@@ -4603,19 +4670,19 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS23" t="n">
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU23" t="n">
         <v>22</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AW23" t="n">
         <v>4</v>
@@ -4630,10 +4697,10 @@
         <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E24" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F24" t="n">
         <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>0.671</v>
+        <v>0.667</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,10 +4750,10 @@
         <v>41.5</v>
       </c>
       <c r="J24" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K24" t="n">
-        <v>0.501</v>
+        <v>0.5</v>
       </c>
       <c r="L24" t="n">
         <v>8.6</v>
@@ -4695,25 +4762,25 @@
         <v>21.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O24" t="n">
         <v>18.8</v>
       </c>
       <c r="P24" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="R24" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U24" t="n">
         <v>26.9</v>
@@ -4722,7 +4789,7 @@
         <v>14.6</v>
       </c>
       <c r="W24" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X24" t="n">
         <v>6.5</v>
@@ -4731,19 +4798,19 @@
         <v>3.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA24" t="n">
         <v>21.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>6</v>
@@ -4755,16 +4822,16 @@
         <v>6</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="n">
         <v>4</v>
@@ -4773,10 +4840,10 @@
         <v>4</v>
       </c>
       <c r="AN24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP24" t="n">
         <v>21</v>
@@ -4788,10 +4855,10 @@
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4800,7 +4867,7 @@
         <v>17</v>
       </c>
       <c r="AW24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4818,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4992,19 @@
         <v>-1.1</v>
       </c>
       <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH25" t="n">
         <v>2</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1</v>
       </c>
       <c r="AI25" t="n">
         <v>27</v>
@@ -4946,7 +5013,7 @@
         <v>22</v>
       </c>
       <c r="AK25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4964,7 +5031,7 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
         <v>18</v>
@@ -4976,10 +5043,10 @@
         <v>24</v>
       </c>
       <c r="AU25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
         <v>30</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5125,7 +5192,7 @@
         <v>14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK26" t="n">
         <v>10</v>
@@ -5137,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -5211,37 +5278,37 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E27" t="n">
         <v>52</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
       </c>
       <c r="I27" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="J27" t="n">
-        <v>78.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L27" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="O27" t="n">
         <v>16.7</v>
@@ -5253,25 +5320,25 @@
         <v>0.764</v>
       </c>
       <c r="R27" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T27" t="n">
         <v>41.4</v>
       </c>
       <c r="U27" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V27" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W27" t="n">
         <v>6.4</v>
       </c>
       <c r="X27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
         <v>4.4</v>
@@ -5280,19 +5347,19 @@
         <v>18.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.8</v>
+        <v>96.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF27" t="n">
         <v>4</v>
@@ -5301,19 +5368,19 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>26</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>28</v>
       </c>
       <c r="AK27" t="n">
         <v>14</v>
       </c>
       <c r="AL27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM27" t="n">
         <v>8</v>
@@ -5340,7 +5407,7 @@
         <v>19</v>
       </c>
       <c r="AU27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AV27" t="n">
         <v>4</v>
@@ -5358,13 +5425,13 @@
         <v>2</v>
       </c>
       <c r="BA27" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB27" t="n">
         <v>24</v>
       </c>
-      <c r="BB27" t="n">
-        <v>25</v>
-      </c>
       <c r="BC27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -5393,61 +5460,61 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G28" t="n">
-        <v>0.224</v>
+        <v>0.227</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="J28" t="n">
         <v>85.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L28" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="O28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="R28" t="n">
         <v>11.8</v>
       </c>
-      <c r="N28" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="O28" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="P28" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="R28" t="n">
-        <v>12</v>
-      </c>
       <c r="S28" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T28" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="U28" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V28" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W28" t="n">
         <v>6.4</v>
@@ -5459,19 +5526,19 @@
         <v>5.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA28" t="n">
         <v>19.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC28" t="n">
         <v>-8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5483,7 +5550,7 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5516,13 +5583,13 @@
         <v>10</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
@@ -5531,19 +5598,19 @@
         <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
         <v>27</v>
       </c>
       <c r="BB28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
         <v>29</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E29" t="n">
         <v>38</v>
       </c>
       <c r="F29" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,40 +5660,40 @@
         <v>38.4</v>
       </c>
       <c r="J29" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.468</v>
+        <v>0.469</v>
       </c>
       <c r="L29" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M29" t="n">
         <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>0.398</v>
+        <v>0.4</v>
       </c>
       <c r="O29" t="n">
         <v>16.4</v>
       </c>
       <c r="P29" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R29" t="n">
         <v>9.5</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U29" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V29" t="n">
         <v>11.8</v>
@@ -5641,31 +5708,31 @@
         <v>4</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB29" t="n">
         <v>100.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5698,7 +5765,7 @@
         <v>27</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5719,13 +5786,13 @@
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -5757,43 +5824,43 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E30" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F30" t="n">
         <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.662</v>
+        <v>0.658</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="J30" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.499</v>
+        <v>0.5</v>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M30" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.38</v>
+        <v>0.377</v>
       </c>
       <c r="O30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P30" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="Q30" t="n">
         <v>0.758</v>
@@ -5802,13 +5869,13 @@
         <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="T30" t="n">
         <v>40.7</v>
       </c>
       <c r="U30" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="V30" t="n">
         <v>14.7</v>
@@ -5823,16 +5890,16 @@
         <v>5.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>106.9</v>
+        <v>107.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5856,13 +5923,13 @@
         <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
       </c>
       <c r="AM30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN30" t="n">
         <v>5</v>
@@ -5889,7 +5956,7 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F31" t="n">
         <v>37</v>
       </c>
       <c r="G31" t="n">
-        <v>0.513</v>
+        <v>0.507</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
@@ -5957,19 +6024,19 @@
         <v>36.4</v>
       </c>
       <c r="J31" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L31" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M31" t="n">
         <v>19.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O31" t="n">
         <v>19.2</v>
@@ -5978,7 +6045,7 @@
         <v>24.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R31" t="n">
         <v>12</v>
@@ -5987,16 +6054,16 @@
         <v>29.2</v>
       </c>
       <c r="T31" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U31" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V31" t="n">
         <v>13.2</v>
       </c>
       <c r="W31" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X31" t="n">
         <v>4.9</v>
@@ -6011,13 +6078,13 @@
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6038,7 +6105,7 @@
         <v>16</v>
       </c>
       <c r="AK31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
         <v>14</v>
@@ -6047,7 +6114,7 @@
         <v>10</v>
       </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6065,7 +6132,7 @@
         <v>26</v>
       </c>
       <c r="AT31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
@@ -6077,13 +6144,13 @@
         <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
         <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA31" t="n">
         <v>22</v>
@@ -6092,7 +6159,7 @@
         <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-4-2007-08</t>
+          <t>2008-04-04</t>
         </is>
       </c>
     </row>
